--- a/01_Thermal/B_results/Single_Fan_Annular_GP/single_annular_gp_summary.xlsx
+++ b/01_Thermal/B_results/Single_Fan_Annular_GP/single_annular_gp_summary.xlsx
@@ -524,29 +524,29 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04993995607641832</v>
+        <v>0.003973611854011006</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1314166511877415</v>
+        <v>0.01534857593669058</v>
       </c>
       <c r="D2" t="n">
-        <v>68.168040044311</v>
+        <v>5.423980180725024</v>
       </c>
       <c r="E2" t="n">
-        <v>23.57400892583172</v>
+        <v>0.3215650391831477</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09502830464586762</v>
+        <v>0.005557203068385242</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9512014842593819</v>
+        <v>0.9993343560411986</v>
       </c>
       <c r="H2" t="n">
         <v>1365</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>cartesian</t>
+          <t>polar</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -555,14 +555,14 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L2" t="b">
         <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>cartesian_matern32_ard_a1</t>
+          <t>polar_matern32_ard_a1p2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -581,11 +581,11 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>-1876.953434387465</v>
+        <v>-1442.125120458416</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.451**2 * Matern(length_scale=[0.154, 0.128, 1.36], nu=1.5) + WhiteKernel(noise_level=0.709)</t>
+          <t>2.61**2 * Matern(length_scale=[0.768, 0.706, 4.99, 0.371], nu=1.5) + WhiteKernel(noise_level=1e-06)</t>
         </is>
       </c>
     </row>
@@ -671,25 +671,25 @@
         <v>195</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08312050824508317</v>
+        <v>0.002851930687344513</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1152251140587861</v>
+        <v>0.007351605213658218</v>
       </c>
       <c r="G2" t="n">
-        <v>16.20849910779122</v>
+        <v>0.5561264840321801</v>
       </c>
       <c r="H2" t="n">
-        <v>2.588981247422754</v>
+        <v>0.0105389893474099</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1296264569840294</v>
+        <v>0.004869212653042428</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9748247643954686</v>
+        <v>0.9998975189410434</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1443758349588905</v>
+        <v>0.02662027479736381</v>
       </c>
     </row>
     <row r="3">
@@ -708,25 +708,25 @@
         <v>195</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03432992508082271</v>
+        <v>0.00314245112357847</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07556559604538518</v>
+        <v>0.01562032444094519</v>
       </c>
       <c r="G3" t="n">
-        <v>6.694335390760429</v>
+        <v>0.6127779690978017</v>
       </c>
       <c r="H3" t="n">
-        <v>1.113481064610395</v>
+        <v>0.04757893444987597</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06149910418711423</v>
+        <v>0.006235304398978792</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9882429686533831</v>
+        <v>0.9994976232272422</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1435290879602334</v>
+        <v>0.02385298967966949</v>
       </c>
     </row>
     <row r="4">
@@ -745,25 +745,25 @@
         <v>195</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06158665835585709</v>
+        <v>0.004467922934874468</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2165059585107317</v>
+        <v>0.01722411271195927</v>
       </c>
       <c r="G4" t="n">
-        <v>12.00939837939213</v>
+        <v>0.8712449723005212</v>
       </c>
       <c r="H4" t="n">
-        <v>9.140591863776882</v>
+        <v>0.05785066144928397</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2168218229579622</v>
+        <v>0.008843279646136596</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8915875668975677</v>
+        <v>0.9993138594242288</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1432121063915787</v>
+        <v>0.02396905577616109</v>
       </c>
     </row>
     <row r="5">
@@ -782,25 +782,25 @@
         <v>195</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05414074143373574</v>
+        <v>0.004855772194503038</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1510342096516959</v>
+        <v>0.01922047628475125</v>
       </c>
       <c r="G5" t="n">
-        <v>10.55744457957847</v>
+        <v>0.9468755779280924</v>
       </c>
       <c r="H5" t="n">
-        <v>4.448209834596925</v>
+        <v>0.0720382081794736</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07060064480189993</v>
+        <v>0.003657129167761755</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9345159163993887</v>
+        <v>0.9989394933642355</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1435030793532903</v>
+        <v>0.01162901138383938</v>
       </c>
     </row>
     <row r="6">
@@ -819,25 +819,25 @@
         <v>195</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04262805076789218</v>
+        <v>0.00412564951207683</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1211394498482411</v>
+        <v>0.0139988334148506</v>
       </c>
       <c r="G6" t="n">
-        <v>8.312469899738975</v>
+        <v>0.8045016548549818</v>
       </c>
       <c r="H6" t="n">
-        <v>2.861579430359229</v>
+        <v>0.03821363071046387</v>
       </c>
       <c r="I6" t="n">
-        <v>0.090542040845843</v>
+        <v>0.006228895889722136</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9380153130043692</v>
+        <v>0.9991722543454762</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1445146759841687</v>
+        <v>0.01917218937407894</v>
       </c>
     </row>
     <row r="7">
@@ -856,25 +856,25 @@
         <v>195</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04058505959188211</v>
+        <v>0.00506226417160916</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1090234332503512</v>
+        <v>0.01941805489630141</v>
       </c>
       <c r="G7" t="n">
-        <v>7.914086620417011</v>
+        <v>0.9871415134637862</v>
       </c>
       <c r="H7" t="n">
-        <v>2.317791254550289</v>
+        <v>0.07352686691137612</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1263612323798324</v>
+        <v>0.01359829008596864</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9544640095972666</v>
+        <v>0.9985554701272401</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1457681901123623</v>
+        <v>0.03352272092573558</v>
       </c>
     </row>
     <row r="8">
@@ -893,25 +893,25 @@
         <v>195</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03318874905965521</v>
+        <v>0.003309292354090562</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07522186774640523</v>
+        <v>0.01057761257908181</v>
       </c>
       <c r="G8" t="n">
-        <v>6.471806066632766</v>
+        <v>0.6453120090476596</v>
       </c>
       <c r="H8" t="n">
-        <v>1.103374230515247</v>
+        <v>0.02181774813526421</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05302902587560862</v>
+        <v>0.004934151793690671</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9693715441463197</v>
+        <v>0.999394363292973</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1472365656759126</v>
+        <v>0.01855130523805199</v>
       </c>
     </row>
   </sheetData>
@@ -925,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cartesian</t>
+          <t>polar</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cartesian_matern32_ard_a1</t>
+          <t>polar_matern32_ard_a1p2</t>
         </is>
       </c>
     </row>
@@ -1142,11 +1142,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>n_restarts_optimizer</t>
+          <t>alpha_jitter</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
     </row>
     <row r="17">
@@ -1155,11 +1155,13 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>random_state</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>42</v>
+          <t>residual_length_scale_floors</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>{'cartesian': [0.55, 0.55, 0.25], 'polar': [0.55, 0.45, 0.45, 0.25], 'radial': [0.55, 0.25]}</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1168,11 +1170,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>autotune_cv_n_splits</t>
+          <t>n_restarts_optimizer</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -1181,11 +1183,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>autotune_cv_restarts_optimizer</t>
+          <t>random_state</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -1194,12 +1196,64 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>autotune_cv_n_splits</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>autotune_cv_restarts_optimizer</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>grid_nx</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>grid_ny</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>kernel_fitted</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0.451**2 * Matern(length_scale=[0.154, 0.128, 1.36], nu=1.5) + WhiteKernel(noise_level=0.709)</t>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2.61**2 * Matern(length_scale=[0.768, 0.706, 4.99, 0.371], nu=1.5) + WhiteKernel(noise_level=1e-06)</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1281,16 +1335,16 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>cartesian_matern32_ard_a1</t>
+          <t>polar_matern32_ard_a1p2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>cartesian</t>
+          <t>polar</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1299,28 +1353,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06256197991048416</v>
+        <v>0.07558426856270242</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1556687793779219</v>
+        <v>0.1739701541993717</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1135156064858128</v>
+        <v>0.1204165072130053</v>
       </c>
       <c r="J2" t="n">
-        <v>85.39710257781088</v>
+        <v>103.1725265880888</v>
       </c>
       <c r="K2" t="n">
-        <v>33.07772951166154</v>
+        <v>41.31256386368907</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05475918323736095</v>
+        <v>-0.1805623356133004</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
@@ -1328,21 +1382,21 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>cartesian_matern52_ard_a1</t>
+          <t>polar_matern32_ard_a1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cartesian</t>
+          <t>polar</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>matern52_ard</t>
+          <t>matern32_ard</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1352,22 +1406,22 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06388187149365782</v>
+        <v>0.07569244469754437</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1567256784974473</v>
+        <v>0.1742297331466416</v>
       </c>
       <c r="I3" t="n">
-        <v>0.113621678743941</v>
+        <v>0.1205818612725141</v>
       </c>
       <c r="J3" t="n">
-        <v>87.19875458884292</v>
+        <v>103.3201870121481</v>
       </c>
       <c r="K3" t="n">
-        <v>33.52841078016233</v>
+        <v>41.43593988035768</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04188035701117998</v>
+        <v>-0.184087972000273</v>
       </c>
       <c r="M3" t="b">
         <v>0</v>
@@ -1375,46 +1429,46 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>polar_matern52_ard_a1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>polar</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>matern52_ard</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>cartesian_rbf_ard_a0p8</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>cartesian</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>rbf_ard</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0.8</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06835437200422528</v>
+        <v>0.07899944579612518</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1615130727643674</v>
+        <v>0.1839709799569285</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1173762863049821</v>
+        <v>0.1272919379110824</v>
       </c>
       <c r="J4" t="n">
-        <v>93.3037177857675</v>
+        <v>107.8342435117109</v>
       </c>
       <c r="K4" t="n">
-        <v>35.60803519972041</v>
+        <v>46.19886380151671</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.01754772085037892</v>
+        <v>-0.32019495890297</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1422,16 +1476,16 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>polar_rbf_ard_a1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cartesian</t>
+          <t>polar</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1446,71 +1500,24 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06857110038297828</v>
+        <v>0.08644309249446497</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1616518060615693</v>
+        <v>0.2100868160088443</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1174550844786755</v>
+        <v>0.1478862805273304</v>
       </c>
       <c r="J5" t="n">
-        <v>93.59955202276537</v>
+        <v>117.9948212549447</v>
       </c>
       <c r="K5" t="n">
-        <v>35.66923324005026</v>
+        <v>60.2462819059019</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.01929653754607341</v>
+        <v>-0.7216189126756771</v>
       </c>
       <c r="M5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>cartesian_rbf_ard_a1p2</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>cartesian</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>rbf_ard</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.06877793824676341</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.1617895362645347</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.1175309252233875</v>
-      </c>
-      <c r="J6" t="n">
-        <v>93.88188570683205</v>
-      </c>
-      <c r="K6" t="n">
-        <v>35.73004077100619</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-0.02103419490873604</v>
-      </c>
-      <c r="M6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1583,16 +1590,16 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>16.20849910779122</v>
+        <v>0.5561264840321801</v>
       </c>
       <c r="E2" t="n">
-        <v>2.588981247422754</v>
+        <v>0.0105389893474099</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1296264569840294</v>
+        <v>0.004869212653042428</v>
       </c>
       <c r="G2" t="n">
-        <v>201.6975596807746</v>
+        <v>0.2845973329614411</v>
       </c>
       <c r="H2" t="n">
         <v>12003.65050354092</v>
@@ -1611,16 +1618,16 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>6.694335390760429</v>
+        <v>0.6127779690978017</v>
       </c>
       <c r="E3" t="n">
-        <v>1.113481064610395</v>
+        <v>0.04757893444987597</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06149910418711423</v>
+        <v>0.006235304398978792</v>
       </c>
       <c r="G3" t="n">
-        <v>37.07704841992418</v>
+        <v>0.3811385650463698</v>
       </c>
       <c r="H3" t="n">
         <v>9803.193489796933</v>
@@ -1639,16 +1646,16 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>12.00939837939213</v>
+        <v>0.8712449723005212</v>
       </c>
       <c r="E4" t="n">
-        <v>9.140591863776882</v>
+        <v>0.05785066144928397</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2168218229579622</v>
+        <v>0.008843279646136596</v>
       </c>
       <c r="G4" t="n">
-        <v>427.3819246160259</v>
+        <v>0.7109464416458999</v>
       </c>
       <c r="H4" t="n">
         <v>9090.968804657296</v>
@@ -1667,16 +1674,16 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>10.55744457957847</v>
+        <v>0.9468755779280924</v>
       </c>
       <c r="E5" t="n">
-        <v>4.448209834596925</v>
+        <v>0.0720382081794736</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07060064480189993</v>
+        <v>0.003657129167761755</v>
       </c>
       <c r="G5" t="n">
-        <v>357.0900572350488</v>
+        <v>0.9581665870669719</v>
       </c>
       <c r="H5" t="n">
         <v>71640.79933933762</v>
@@ -1695,16 +1702,16 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>8.312469899738975</v>
+        <v>0.8045016548549818</v>
       </c>
       <c r="E6" t="n">
-        <v>2.861579430359229</v>
+        <v>0.03821363071046387</v>
       </c>
       <c r="F6" t="n">
-        <v>0.090542040845843</v>
+        <v>0.006228895889722136</v>
       </c>
       <c r="G6" t="n">
-        <v>131.548354232224</v>
+        <v>0.6225969724945055</v>
       </c>
       <c r="H6" t="n">
         <v>16046.66774128612</v>
@@ -1723,16 +1730,16 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>7.914086620417011</v>
+        <v>0.9871415134637862</v>
       </c>
       <c r="E7" t="n">
-        <v>2.317791254550289</v>
+        <v>0.07352686691137612</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1263612323798324</v>
+        <v>0.01359829008596864</v>
       </c>
       <c r="G7" t="n">
-        <v>86.28744571366516</v>
+        <v>0.9992830261476681</v>
       </c>
       <c r="H7" t="n">
         <v>5404.056829595331</v>
@@ -1751,16 +1758,16 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>6.471806066632766</v>
+        <v>0.6453120090476596</v>
       </c>
       <c r="E8" t="n">
-        <v>1.103374230515247</v>
+        <v>0.02181774813526421</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05302902587560862</v>
+        <v>0.004934151793690671</v>
       </c>
       <c r="G8" t="n">
-        <v>54.90554248283681</v>
+        <v>0.4753504397745663</v>
       </c>
       <c r="H8" t="n">
         <v>19524.90314262348</v>
@@ -1777,16 +1784,16 @@
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>68.168040044311</v>
+        <v>5.423980180725023</v>
       </c>
       <c r="E9" t="n">
-        <v>23.57400892583172</v>
+        <v>0.3215650391831476</v>
       </c>
       <c r="F9" t="n">
-        <v>0.09502830464586762</v>
+        <v>0.005557203068385242</v>
       </c>
       <c r="G9" t="n">
-        <v>1295.987932380499</v>
+        <v>4.432079365137422</v>
       </c>
       <c r="H9" t="n">
         <v>143514.2398508377</v>

--- a/01_Thermal/B_results/Single_Fan_Annular_GP/single_annular_gp_summary.xlsx
+++ b/01_Thermal/B_results/Single_Fan_Annular_GP/single_annular_gp_summary.xlsx
@@ -524,22 +524,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.003973611854011006</v>
+        <v>0.004495361034736806</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01534857593669058</v>
+        <v>0.01614020917637711</v>
       </c>
       <c r="D2" t="n">
-        <v>5.423980180725024</v>
+        <v>6.13616781241574</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3215650391831477</v>
+        <v>0.3555911708310888</v>
       </c>
       <c r="F2" t="n">
-        <v>0.005557203068385242</v>
+        <v>0.006072726408910501</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9993343560411986</v>
+        <v>0.9992639214907563</v>
       </c>
       <c r="H2" t="n">
         <v>1365</v>
@@ -581,11 +581,11 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>-1442.125120458416</v>
+        <v>-1470.171428572352</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2.61**2 * Matern(length_scale=[0.768, 0.706, 4.99, 0.371], nu=1.5) + WhiteKernel(noise_level=1e-06)</t>
+          <t>2.29**2 * Matern(length_scale=[0.716, 0.659, 3.7, 0.371], nu=1.5) + WhiteKernel(noise_level=1e-06)</t>
         </is>
       </c>
     </row>
@@ -671,25 +671,25 @@
         <v>195</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002851930687344513</v>
+        <v>0.002740228034346805</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007351605213658218</v>
+        <v>0.006228954140159761</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5561264840321801</v>
+        <v>0.5343444666976269</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0105389893474099</v>
+        <v>0.007565974587641617</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004869212653042428</v>
+        <v>0.003222045510534377</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9998975189410434</v>
+        <v>0.9999264285158452</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02662027479736381</v>
+        <v>0.02141624693338006</v>
       </c>
     </row>
     <row r="3">
@@ -708,25 +708,25 @@
         <v>195</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00314245112357847</v>
+        <v>0.003876092960394641</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01562032444094519</v>
+        <v>0.01439912029666496</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6127779690978017</v>
+        <v>0.755838127276955</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04757893444987597</v>
+        <v>0.04043025973697661</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006235304398978792</v>
+        <v>0.006931189678378079</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9994976232272422</v>
+        <v>0.9995731047018336</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02385298967966949</v>
+        <v>0.03068080497682862</v>
       </c>
     </row>
     <row r="4">
@@ -745,25 +745,25 @@
         <v>195</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004467922934874468</v>
+        <v>0.005661167651299266</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01722411271195927</v>
+        <v>0.02659476931518984</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8712449723005212</v>
+        <v>1.103927692003357</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05785066144928397</v>
+        <v>0.1379199422109918</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008843279646136596</v>
+        <v>0.01006828969462627</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9993138594242288</v>
+        <v>0.9983641938365397</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02396905577616109</v>
+        <v>0.02048683276957119</v>
       </c>
     </row>
     <row r="5">
@@ -782,25 +782,25 @@
         <v>195</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004855772194503038</v>
+        <v>0.004568449907610159</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01922047628475125</v>
+        <v>0.01353455015887957</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9468755779280924</v>
+        <v>0.8908477319839812</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0720382081794736</v>
+        <v>0.03572088936062925</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003657129167761755</v>
+        <v>0.003900189459186168</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9989394933642355</v>
+        <v>0.9994741368343313</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01162901138383938</v>
+        <v>0.01887501443783774</v>
       </c>
     </row>
     <row r="6">
@@ -819,25 +819,25 @@
         <v>195</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00412564951207683</v>
+        <v>0.003036444370699831</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0139988334148506</v>
+        <v>0.007075312931628944</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8045016548549818</v>
+        <v>0.5921066522864671</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03821363071046387</v>
+        <v>0.009761710350692772</v>
       </c>
       <c r="I6" t="n">
-        <v>0.006228895889722136</v>
+        <v>0.004646044913083442</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9991722543454762</v>
+        <v>0.9997885515410789</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01917218937407894</v>
+        <v>0.01939271927210885</v>
       </c>
     </row>
     <row r="7">
@@ -856,25 +856,25 @@
         <v>195</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00506226417160916</v>
+        <v>0.005644992217931454</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01941805489630141</v>
+        <v>0.02062927503981881</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9871415134637862</v>
+        <v>1.100773482496634</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07352686691137612</v>
+        <v>0.08298556279035579</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01359829008596864</v>
+        <v>0.01043674211344744</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9985554701272401</v>
+        <v>0.9983696418806618</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03352272092573558</v>
+        <v>0.0288619714927124</v>
       </c>
     </row>
     <row r="8">
@@ -893,25 +893,25 @@
         <v>195</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003309292354090562</v>
+        <v>0.005940152100875487</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01057761257908181</v>
+        <v>0.0145367495033125</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6453120090476596</v>
+        <v>1.15832965967072</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02181774813526421</v>
+        <v>0.04120683179380095</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004934151793690671</v>
+        <v>0.00893957838027405</v>
       </c>
       <c r="J8" t="n">
-        <v>0.999394363292973</v>
+        <v>0.9988561436423279</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01855130523805199</v>
+        <v>0.027851653761143</v>
       </c>
     </row>
   </sheetData>
@@ -925,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1142,11 +1142,13 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>alpha_jitter</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1e-08</v>
+          <t>sigma_mapping_method</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>annular_nearest_radius + z_pchip_hold_bounds</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1155,13 +1157,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>residual_length_scale_floors</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'cartesian': [0.55, 0.55, 0.25], 'polar': [0.55, 0.45, 0.45, 0.25], 'radial': [0.55, 0.25]}</t>
-        </is>
+          <t>alpha_jitter</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1e-08</v>
       </c>
     </row>
     <row r="18">
@@ -1170,11 +1170,13 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>n_restarts_optimizer</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>6</v>
+          <t>residual_length_scale_floors</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>{'cartesian': [0.55, 0.55, 0.25], 'polar': [0.55, 0.45, 0.45, 0.25], 'radial': [0.55, 0.25]}</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1183,11 +1185,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>random_state</t>
+          <t>n_restarts_optimizer</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -1196,11 +1198,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>autotune_cv_n_splits</t>
+          <t>random_state</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21">
@@ -1209,11 +1211,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>autotune_cv_restarts_optimizer</t>
+          <t>autotune_cv_n_splits</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1222,11 +1224,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>grid_nx</t>
+          <t>autotune_cv_restarts_optimizer</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>240</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1235,11 +1237,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>grid_ny</t>
+          <t>grid_nx</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24">
@@ -1248,12 +1250,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>grid_ny</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>overall_fluctuation_rule</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>sqrt(sigma_fluc_mps^2 + w_pred_std_mps^2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>kernel_fitted</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2.61**2 * Matern(length_scale=[0.768, 0.706, 4.99, 0.371], nu=1.5) + WhiteKernel(noise_level=1e-06)</t>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2.29**2 * Matern(length_scale=[0.716, 0.659, 3.7, 0.371], nu=1.5) + WhiteKernel(noise_level=1e-06)</t>
         </is>
       </c>
     </row>
@@ -1359,22 +1389,22 @@
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07558426856270242</v>
+        <v>0.064225898294338</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1739701541993717</v>
+        <v>0.160871847108765</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1204165072130053</v>
+        <v>0.1080510247691619</v>
       </c>
       <c r="J2" t="n">
-        <v>103.1725265880888</v>
+        <v>87.66835117177138</v>
       </c>
       <c r="K2" t="n">
-        <v>41.31256386368907</v>
+        <v>35.32586037733368</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.1805623356133004</v>
+        <v>-0.1593683091575866</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
@@ -1406,22 +1436,22 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07569244469754437</v>
+        <v>0.06435532014769701</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1742297331466416</v>
+        <v>0.1612459995772764</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1205818612725141</v>
+        <v>0.1083021886295799</v>
       </c>
       <c r="J3" t="n">
-        <v>103.3201870121481</v>
+        <v>87.84501200160642</v>
       </c>
       <c r="K3" t="n">
-        <v>41.43593988035768</v>
+        <v>35.49037179825642</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.184087972000273</v>
+        <v>-0.1647674509159198</v>
       </c>
       <c r="M3" t="b">
         <v>0</v>
@@ -1453,22 +1483,22 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07899944579612518</v>
+        <v>0.0671941633377675</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1839709799569285</v>
+        <v>0.1696571806464321</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1272919379110824</v>
+        <v>0.1126189793245894</v>
       </c>
       <c r="J4" t="n">
-        <v>107.8342435117109</v>
+        <v>91.72003295605263</v>
       </c>
       <c r="K4" t="n">
-        <v>46.19886380151671</v>
+        <v>39.28955795978317</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.32019495890297</v>
+        <v>-0.2894538984423429</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1500,22 +1530,22 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08644309249446497</v>
+        <v>0.07368010751612095</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2100868160088443</v>
+        <v>0.1885409889873067</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1478862805273304</v>
+        <v>0.1230656778367653</v>
       </c>
       <c r="J5" t="n">
-        <v>117.9948212549447</v>
+        <v>100.5733467595051</v>
       </c>
       <c r="K5" t="n">
-        <v>60.2462819059019</v>
+        <v>48.52261668114549</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7216189126756771</v>
+        <v>-0.5924759781255584</v>
       </c>
       <c r="M5" t="b">
         <v>0</v>
@@ -1590,19 +1620,19 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5561264840321801</v>
+        <v>0.5343444666976269</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0105389893474099</v>
+        <v>0.007565974587641617</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004869212653042428</v>
+        <v>0.003222045510534377</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2845973329614411</v>
+        <v>0.260528177924342</v>
       </c>
       <c r="H2" t="n">
-        <v>12003.65050354092</v>
+        <v>25095.24045331192</v>
       </c>
     </row>
     <row r="3">
@@ -1618,19 +1648,19 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6127779690978017</v>
+        <v>0.755838127276955</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04757893444987597</v>
+        <v>0.04043025973697661</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006235304398978792</v>
+        <v>0.006931189678378079</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3811385650463698</v>
+        <v>0.3313409068848943</v>
       </c>
       <c r="H3" t="n">
-        <v>9803.193489796933</v>
+        <v>6896.988293181215</v>
       </c>
     </row>
     <row r="4">
@@ -1646,19 +1676,19 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8712449723005212</v>
+        <v>1.103927692003357</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05785066144928397</v>
+        <v>0.1379199422109918</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008843279646136596</v>
+        <v>0.01006828969462627</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7109464416458999</v>
+        <v>1.188232215803369</v>
       </c>
       <c r="H4" t="n">
-        <v>9090.968804657296</v>
+        <v>11721.6815093248</v>
       </c>
     </row>
     <row r="5">
@@ -1674,19 +1704,19 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9468755779280924</v>
+        <v>0.8908477319839812</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0720382081794736</v>
+        <v>0.03572088936062925</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003657129167761755</v>
+        <v>0.003900189459186168</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9581665870669719</v>
+        <v>0.6963057632461083</v>
       </c>
       <c r="H5" t="n">
-        <v>71640.79933933762</v>
+        <v>45775.02407050147</v>
       </c>
     </row>
     <row r="6">
@@ -1702,19 +1732,19 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8045016548549818</v>
+        <v>0.5921066522864671</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03821363071046387</v>
+        <v>0.009761710350692772</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006228895889722136</v>
+        <v>0.004646044913083442</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6225969724945055</v>
+        <v>0.3492696160339002</v>
       </c>
       <c r="H6" t="n">
-        <v>16046.66774128612</v>
+        <v>16180.57680150592</v>
       </c>
     </row>
     <row r="7">
@@ -1730,19 +1760,19 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9871415134637862</v>
+        <v>1.100773482496634</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07352686691137612</v>
+        <v>0.08298556279035579</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01359829008596864</v>
+        <v>0.01043674211344744</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9992830261476681</v>
+        <v>1.065387561065905</v>
       </c>
       <c r="H7" t="n">
-        <v>5404.056829595331</v>
+        <v>9780.875189666229</v>
       </c>
     </row>
     <row r="8">
@@ -1758,19 +1788,19 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6453120090476596</v>
+        <v>1.15832965967072</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02181774813526421</v>
+        <v>0.04120683179380095</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004934151793690671</v>
+        <v>0.00893957838027405</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4753504397745663</v>
+        <v>0.6805720908328852</v>
       </c>
       <c r="H8" t="n">
-        <v>19524.90314262348</v>
+        <v>8516.086466998437</v>
       </c>
     </row>
     <row r="9">
@@ -1784,19 +1814,19 @@
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>5.423980180725023</v>
+        <v>6.13616781241574</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3215650391831476</v>
+        <v>0.3555911708310888</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005557203068385242</v>
+        <v>0.006072726408910501</v>
       </c>
       <c r="G9" t="n">
-        <v>4.432079365137422</v>
+        <v>4.571636331791403</v>
       </c>
       <c r="H9" t="n">
-        <v>143514.2398508377</v>
+        <v>123966.47278449</v>
       </c>
     </row>
   </sheetData>
